--- a/data/trans_orig/P16A11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82039</t>
+          <t>80783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118799</t>
+          <t>117626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>93892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134975</t>
+          <t>134756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189107</t>
+          <t>188207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241629</t>
+          <t>240857</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574195</t>
+          <t>575368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>610955</t>
+          <t>612211</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>553376</t>
+          <t>553595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>591713</t>
+          <t>594459</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1139716</t>
+          <t>1140488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1192238</t>
+          <t>1193138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101424</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144062</t>
+          <t>143151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148786</t>
+          <t>148682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>195915</t>
+          <t>196997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259992</t>
+          <t>259513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322977</t>
+          <t>323739</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>817738</t>
+          <t>818649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>860376</t>
+          <t>859996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>772478</t>
+          <t>771396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>819607</t>
+          <t>819711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1607216</t>
+          <t>1606454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1670201</t>
+          <t>1670680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70262</t>
+          <t>66920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104114</t>
+          <t>104350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96698</t>
+          <t>97197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134600</t>
+          <t>136296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>178818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231075</t>
+          <t>229299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574395</t>
+          <t>574159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608247</t>
+          <t>611589</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549241</t>
+          <t>547545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587143</t>
+          <t>586644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1131275</t>
+          <t>1133051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1185703</t>
+          <t>1183532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88949</t>
+          <t>89627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>125324</t>
+          <t>128297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141071</t>
+          <t>139513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188440</t>
+          <t>187191</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240637</t>
+          <t>241345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>298693</t>
+          <t>299853</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>816898</t>
+          <t>813925</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>853273</t>
+          <t>852595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>850172</t>
+          <t>851421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>897541</t>
+          <t>899099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1682141</t>
+          <t>1680981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1740197</t>
+          <t>1739489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379776</t>
+          <t>379184</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>455223</t>
+          <t>449429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520780</t>
+          <t>525033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>611006</t>
+          <t>608714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>920899</t>
+          <t>922669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1037997</t>
+          <t>1040186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2820302</t>
+          <t>2826096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2895749</t>
+          <t>2896341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2768191</t>
+          <t>2770483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2858417</t>
+          <t>2854164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5616725</t>
+          <t>5614536</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5733823</t>
+          <t>5732053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112889</t>
+          <t>112680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155450</t>
+          <t>153635</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145429</t>
+          <t>145184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191150</t>
+          <t>191001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270776</t>
+          <t>270844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>333408</t>
+          <t>332329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>546129</t>
+          <t>547944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588690</t>
+          <t>588899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>504181</t>
+          <t>504330</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>549902</t>
+          <t>550147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1063502</t>
+          <t>1064581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1126134</t>
+          <t>1126066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128172</t>
+          <t>127583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175818</t>
+          <t>176302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168721</t>
+          <t>166220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220015</t>
+          <t>218332</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311931</t>
+          <t>308861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>380725</t>
+          <t>379155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>842129</t>
+          <t>841645</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>889775</t>
+          <t>890364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>806635</t>
+          <t>808318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>857929</t>
+          <t>860430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1663872</t>
+          <t>1665442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1732666</t>
+          <t>1735736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93350</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>136682</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114791</t>
+          <t>115357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>158916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222816</t>
+          <t>220334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>280426</t>
+          <t>282006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619856</t>
+          <t>623471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663188</t>
+          <t>664235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617315</t>
+          <t>617367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661492</t>
+          <t>660926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252395</t>
+          <t>1250815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1310005</t>
+          <t>1312487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149915</t>
+          <t>149704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198571</t>
+          <t>198213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217023</t>
+          <t>219335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273855</t>
+          <t>275713</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384730</t>
+          <t>379513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459106</t>
+          <t>458211</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>747359</t>
+          <t>747717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>796015</t>
+          <t>796226</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>774908</t>
+          <t>773050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>831740</t>
+          <t>829428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1535588</t>
+          <t>1536483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1609964</t>
+          <t>1615181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>521960</t>
+          <t>527150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>617425</t>
+          <t>617562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>695928</t>
+          <t>693845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>791566</t>
+          <t>796944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1243721</t>
+          <t>1249357</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1377777</t>
+          <t>1382581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2804569</t>
+          <t>2804432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2900034</t>
+          <t>2894844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2755462</t>
+          <t>2750084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2851100</t>
+          <t>2853183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5591244</t>
+          <t>5586440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5725300</t>
+          <t>5719664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85521</t>
+          <t>85968</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122877</t>
+          <t>121577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113269</t>
+          <t>111524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153703</t>
+          <t>152684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209199</t>
+          <t>210096</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>263810</t>
+          <t>264320</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>551923</t>
+          <t>553223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>589279</t>
+          <t>588832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519136</t>
+          <t>520155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559570</t>
+          <t>561315</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1083829</t>
+          <t>1083319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1138440</t>
+          <t>1137543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123324</t>
+          <t>125350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169828</t>
+          <t>170998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148221</t>
+          <t>152272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>201891</t>
+          <t>204864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288576</t>
+          <t>282806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357730</t>
+          <t>356929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>852603</t>
+          <t>851433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>899107</t>
+          <t>897081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>841022</t>
+          <t>838049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>894692</t>
+          <t>890641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1707614</t>
+          <t>1708415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1776768</t>
+          <t>1782538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91225</t>
+          <t>89224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131992</t>
+          <t>132240</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122828</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170693</t>
+          <t>171800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230017</t>
+          <t>225937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288705</t>
+          <t>292037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627560</t>
+          <t>627312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668327</t>
+          <t>670328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614318</t>
+          <t>613211</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>662183</t>
+          <t>661332</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255858</t>
+          <t>1252526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314546</t>
+          <t>1318626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123011</t>
+          <t>123206</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>166298</t>
+          <t>165727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153145</t>
+          <t>153736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207290</t>
+          <t>206681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286211</t>
+          <t>289572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361152</t>
+          <t>353129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771269</t>
+          <t>771840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814556</t>
+          <t>814361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>836489</t>
+          <t>837098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>890634</t>
+          <t>890043</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1620194</t>
+          <t>1628217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1695135</t>
+          <t>1691774</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>464438</t>
+          <t>464682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>550516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582339</t>
+          <t>582402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>677238</t>
+          <t>675898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1072519</t>
+          <t>1071688</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1202296</t>
+          <t>1196193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2847771</t>
+          <t>2843834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2929912</t>
+          <t>2929668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2867304</t>
+          <t>2868644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2962203</t>
+          <t>2962140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5736596</t>
+          <t>5742699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5866373</t>
+          <t>5867204</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>115589</t>
+          <t>113607</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153367</t>
+          <t>151244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143595</t>
+          <t>142911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174896</t>
+          <t>172514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>266141</t>
+          <t>268235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>316535</t>
+          <t>314436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482074</t>
+          <t>484197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>519852</t>
+          <t>521834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>500856</t>
+          <t>503238</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>532157</t>
+          <t>532841</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>994659</t>
+          <t>996758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1045053</t>
+          <t>1042959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,54%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89010</t>
+          <t>71036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208703</t>
+          <t>207918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161837</t>
+          <t>161621</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197152</t>
+          <t>198462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219535</t>
+          <t>227038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391463</t>
+          <t>391081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984161</t>
+          <t>984946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1103854</t>
+          <t>1121828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>760954</t>
+          <t>759644</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>796269</t>
+          <t>796485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1759508</t>
+          <t>1759890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1931436</t>
+          <t>1923933</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116817</t>
+          <t>116571</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158159</t>
+          <t>158263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141320</t>
+          <t>142851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>608433</t>
+          <t>653803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278264</t>
+          <t>278657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>909961</t>
+          <t>820927</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544641</t>
+          <t>544537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585983</t>
+          <t>586229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324367</t>
+          <t>278997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>791480</t>
+          <t>789949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>725639</t>
+          <t>814673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1357336</t>
+          <t>1356943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,96%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164444</t>
+          <t>162163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209811</t>
+          <t>208688</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201303</t>
+          <t>196850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273606</t>
+          <t>272702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378545</t>
+          <t>378560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>465910</t>
+          <t>462586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>717020</t>
+          <t>718143</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>762387</t>
+          <t>764668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817768</t>
+          <t>818672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>890071</t>
+          <t>894524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1552295</t>
+          <t>1555619</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639660</t>
+          <t>1639645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>472651</t>
+          <t>468711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>672069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>724417</t>
+          <t>721775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1439981</t>
+          <t>1386413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1316310</t>
+          <t>1305539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2143246</t>
+          <t>2162816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2779575</t>
+          <t>2785868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2985286</t>
+          <t>2989226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2218052</t>
+          <t>2271620</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2933616</t>
+          <t>2936258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4972723</t>
+          <t>4953153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5799659</t>
+          <t>5810430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80783</t>
+          <t>80057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117626</t>
+          <t>115615</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93892</t>
+          <t>97975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134756</t>
+          <t>135167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188207</t>
+          <t>187547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>240857</t>
+          <t>238766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575368</t>
+          <t>577379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>612211</t>
+          <t>612937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>553595</t>
+          <t>553184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>594459</t>
+          <t>590376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1140488</t>
+          <t>1142579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1193138</t>
+          <t>1193798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101804</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143151</t>
+          <t>143938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>146751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>196997</t>
+          <t>195729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259513</t>
+          <t>262271</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323739</t>
+          <t>324090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>818649</t>
+          <t>817862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>859996</t>
+          <t>858429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>771396</t>
+          <t>772664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>819711</t>
+          <t>821642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1606454</t>
+          <t>1606103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1670680</t>
+          <t>1667922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66920</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104350</t>
+          <t>104228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97197</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136296</t>
+          <t>134398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178818</t>
+          <t>177408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229299</t>
+          <t>228993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>574159</t>
+          <t>574281</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>611589</t>
+          <t>608448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>547545</t>
+          <t>549443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>586644</t>
+          <t>587635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1133051</t>
+          <t>1133357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1183532</t>
+          <t>1184942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89627</t>
+          <t>89658</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128297</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139513</t>
+          <t>140051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187191</t>
+          <t>186752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241345</t>
+          <t>236902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>299853</t>
+          <t>299097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>813925</t>
+          <t>816037</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852595</t>
+          <t>852564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>851421</t>
+          <t>851860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899099</t>
+          <t>898561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1680981</t>
+          <t>1681737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1739489</t>
+          <t>1743932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>379184</t>
+          <t>380247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>449429</t>
+          <t>452546</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>525033</t>
+          <t>524789</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>608714</t>
+          <t>611644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>922669</t>
+          <t>915783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1040186</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2826096</t>
+          <t>2822979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2896341</t>
+          <t>2895278</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2770483</t>
+          <t>2767553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2854164</t>
+          <t>2854408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5614536</t>
+          <t>5625785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5732053</t>
+          <t>5738939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112680</t>
+          <t>112381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153635</t>
+          <t>153263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>144947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>191001</t>
+          <t>190358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270844</t>
+          <t>270497</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332329</t>
+          <t>337085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>547944</t>
+          <t>548316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588899</t>
+          <t>589198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>504330</t>
+          <t>504973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550147</t>
+          <t>550384</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1064581</t>
+          <t>1059825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1126066</t>
+          <t>1126413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>127583</t>
+          <t>129951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176302</t>
+          <t>178327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166220</t>
+          <t>166184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>218332</t>
+          <t>219012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308861</t>
+          <t>311470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379155</t>
+          <t>377596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>841645</t>
+          <t>839620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>890364</t>
+          <t>887996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>808318</t>
+          <t>807638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>860430</t>
+          <t>860466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1665442</t>
+          <t>1667001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1735736</t>
+          <t>1733127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92303</t>
+          <t>92234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133067</t>
+          <t>135333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>112803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158916</t>
+          <t>158020</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220334</t>
+          <t>220408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282006</t>
+          <t>279955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623471</t>
+          <t>621205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664235</t>
+          <t>664304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>617367</t>
+          <t>618263</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660926</t>
+          <t>663480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1250815</t>
+          <t>1252866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1312487</t>
+          <t>1312413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149704</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198213</t>
+          <t>199748</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219335</t>
+          <t>216409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275713</t>
+          <t>272171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>379513</t>
+          <t>384360</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>458211</t>
+          <t>460344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>747717</t>
+          <t>746182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>796226</t>
+          <t>797206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>773050</t>
+          <t>776592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>829428</t>
+          <t>832354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1536483</t>
+          <t>1534350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1615181</t>
+          <t>1610334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>527150</t>
+          <t>526209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>617562</t>
+          <t>616452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>693845</t>
+          <t>690133</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>796944</t>
+          <t>794399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1249357</t>
+          <t>1249622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1382581</t>
+          <t>1381315</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2804432</t>
+          <t>2805542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2894844</t>
+          <t>2895785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2750084</t>
+          <t>2752629</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2853183</t>
+          <t>2856895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5586440</t>
+          <t>5587706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5719664</t>
+          <t>5719399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85968</t>
+          <t>86181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121577</t>
+          <t>122160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111524</t>
+          <t>111022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152684</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210096</t>
+          <t>206788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>264320</t>
+          <t>263552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>553223</t>
+          <t>552640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>588832</t>
+          <t>588619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>520155</t>
+          <t>520037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>561315</t>
+          <t>561817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1083319</t>
+          <t>1084087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1137543</t>
+          <t>1140851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125350</t>
+          <t>127700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170998</t>
+          <t>173479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>152272</t>
+          <t>150173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204864</t>
+          <t>199319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>282806</t>
+          <t>287211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>356929</t>
+          <t>356009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>851433</t>
+          <t>848952</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>897081</t>
+          <t>894731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>838049</t>
+          <t>843594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>890641</t>
+          <t>892740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1708415</t>
+          <t>1709335</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1782538</t>
+          <t>1778133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89224</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132240</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123679</t>
+          <t>122099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171800</t>
+          <t>169485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225937</t>
+          <t>223678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292037</t>
+          <t>287735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627312</t>
+          <t>628295</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>670328</t>
+          <t>667193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>613211</t>
+          <t>615526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661332</t>
+          <t>662912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252526</t>
+          <t>1256828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1318626</t>
+          <t>1320885</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123206</t>
+          <t>122285</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165727</t>
+          <t>165363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153736</t>
+          <t>153272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206681</t>
+          <t>206574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>289572</t>
+          <t>288810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353129</t>
+          <t>355986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771840</t>
+          <t>772204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814361</t>
+          <t>815282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>837098</t>
+          <t>837205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>890043</t>
+          <t>890507</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1628217</t>
+          <t>1625360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1691774</t>
+          <t>1692536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>464682</t>
+          <t>460657</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>550516</t>
+          <t>542765</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582402</t>
+          <t>581873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>675898</t>
+          <t>681888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1071688</t>
+          <t>1072991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1196193</t>
+          <t>1201570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2843834</t>
+          <t>2851585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2929668</t>
+          <t>2933693</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2868644</t>
+          <t>2862654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2962140</t>
+          <t>2962669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5742699</t>
+          <t>5737322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5867204</t>
+          <t>5865901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>132854</t>
+          <t>143322</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113607</t>
+          <t>123840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>165862</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>157596</t>
+          <t>167390</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142911</t>
+          <t>152286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>172514</t>
+          <t>183315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>290450</t>
+          <t>310712</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>268235</t>
+          <t>284605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314436</t>
+          <t>337787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>502587</t>
+          <t>547388</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484197</t>
+          <t>524848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>521834</t>
+          <t>566870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>518156</t>
+          <t>565723</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>503238</t>
+          <t>549798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>532841</t>
+          <t>580827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1020744</t>
+          <t>1113111</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>996758</t>
+          <t>1086036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1042959</t>
+          <t>1139218</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>159020</t>
+          <t>173582</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71036</t>
+          <t>152567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207918</t>
+          <t>199824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179287</t>
+          <t>199794</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161621</t>
+          <t>180461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198462</t>
+          <t>219846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>373376</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227038</t>
+          <t>345498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>391081</t>
+          <t>406754</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1033844</t>
+          <t>875335</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984946</t>
+          <t>849093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121828</t>
+          <t>896350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>778819</t>
+          <t>871044</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>759644</t>
+          <t>850992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>796485</t>
+          <t>890377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1812663</t>
+          <t>1746379</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1759890</t>
+          <t>1713001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1923933</t>
+          <t>1774257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136621</t>
+          <t>155829</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116571</t>
+          <t>133358</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158263</t>
+          <t>180272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>321718</t>
+          <t>137821</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142851</t>
+          <t>120737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>653803</t>
+          <t>156231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>458340</t>
+          <t>293650</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278657</t>
+          <t>265707</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>820927</t>
+          <t>321762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>566179</t>
+          <t>645334</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544537</t>
+          <t>620891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586229</t>
+          <t>667805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>611082</t>
+          <t>673842</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278997</t>
+          <t>655432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>789949</t>
+          <t>690926</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1177260</t>
+          <t>1319176</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814673</t>
+          <t>1291064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1356943</t>
+          <t>1347119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702800</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702800</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702800</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932800</t>
+          <t>811663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635600</t>
+          <t>1612826</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635600</t>
+          <t>1612826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635600</t>
+          <t>1612826</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>184843</t>
+          <t>190347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162163</t>
+          <t>167377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208688</t>
+          <t>214543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>244039</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196850</t>
+          <t>239292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272702</t>
+          <t>286562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>428882</t>
+          <t>451565</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378560</t>
+          <t>421816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462586</t>
+          <t>485429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>741988</t>
+          <t>799715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>718143</t>
+          <t>775519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>764668</t>
+          <t>822685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>847335</t>
+          <t>855813</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>818672</t>
+          <t>830469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>894524</t>
+          <t>877739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1589323</t>
+          <t>1655528</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1555619</t>
+          <t>1621664</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639645</t>
+          <t>1685277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>468711</t>
+          <t>618741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>672069</t>
+          <t>705213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>721775</t>
+          <t>726964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1386413</t>
+          <t>803573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1305539</t>
+          <t>1369921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2162816</t>
+          <t>1483872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2844598</t>
+          <t>2867772</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2785868</t>
+          <t>2825639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2989226</t>
+          <t>2912111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2755392</t>
+          <t>2966423</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2271620</t>
+          <t>2929072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2936258</t>
+          <t>3005681</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5599990</t>
+          <t>5834195</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4953153</t>
+          <t>5779625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5810430</t>
+          <t>5893576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
